--- a/账号管理.xlsx
+++ b/账号管理.xlsx
@@ -10,6 +10,7 @@
     <sheet name="写手" sheetId="1" r:id="rId1"/>
     <sheet name="用户" sheetId="2" r:id="rId2"/>
     <sheet name="平台" sheetId="3" r:id="rId3"/>
+    <sheet name="监管" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="88">
   <si>
     <t>账号</t>
   </si>
@@ -260,6 +261,39 @@
   </si>
   <si>
     <t>pingtai2</t>
+  </si>
+  <si>
+    <t>platform3</t>
+  </si>
+  <si>
+    <t>pingtai3</t>
+  </si>
+  <si>
+    <t>platform4</t>
+  </si>
+  <si>
+    <t>pingtai4</t>
+  </si>
+  <si>
+    <t>负责平台</t>
+  </si>
+  <si>
+    <t>regulator1</t>
+  </si>
+  <si>
+    <t>jianguan1</t>
+  </si>
+  <si>
+    <t>[0,1]</t>
+  </si>
+  <si>
+    <t>regulator2</t>
+  </si>
+  <si>
+    <t>jianguan2</t>
+  </si>
+  <si>
+    <t>[2,3]</t>
   </si>
 </sst>
 </file>
@@ -1728,10 +1762,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="2"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="10.5929203539823" customWidth="1"/>
+    <col min="4" max="4" width="11.1592920353982" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1767,6 +1802,77 @@
         <v>1</v>
       </c>
     </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="10.5929203539823" customWidth="1"/>
+    <col min="2" max="2" width="9.53097345132743" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
